--- a/test-data/Template_Master_Test_Suite.xlsx
+++ b/test-data/Template_Master_Test_Suite.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +71,15 @@
       <name val="Consolas"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -91,8 +98,20 @@
         <bgColor rgb="FFF3F4F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3A4A"/>
+        <bgColor rgb="001A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+        <bgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,12 +134,18 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,12 +194,58 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -227,6 +298,28 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -629,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="21.26953125" customWidth="1" style="2" min="1" max="1"/>
@@ -649,934 +742,934 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>tc-id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>expected</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>[o]_observed</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>[o]_test_result</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>[o]_screenshot</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>[o]_duration_(s)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>TC_LOGIN_001</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Đăng nhập thành công và chọn Bệnh viện</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>navigate</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>url_sit_login</t>
         </is>
       </c>
-      <c r="G2" s="14" t="n"/>
-      <c r="H2" s="12" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
+      <c r="G2" s="23" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="24" t="n"/>
+      <c r="J2" s="24" t="n"/>
+      <c r="K2" s="24" t="n"/>
+      <c r="L2" s="24" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="13" t="n">
+      <c r="A3" s="19" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>click</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>btn_sit_login</t>
         </is>
       </c>
-      <c r="G3" s="14" t="n"/>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="24" t="n"/>
+      <c r="J3" s="24" t="n"/>
+      <c r="K3" s="24" t="n"/>
+      <c r="L3" s="24" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="13" t="n">
+      <c r="A4" s="19" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>txt_username</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>$data_login.username</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="24" t="n"/>
+      <c r="J4" s="24" t="n"/>
+      <c r="K4" s="24" t="n"/>
+      <c r="L4" s="24" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="13" t="n">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>txt_password</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>$data_login.password</t>
         </is>
       </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="24" t="n"/>
+      <c r="J5" s="24" t="n"/>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="13" t="n">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>click</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>btn_login</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="24" t="n"/>
+      <c r="L6" s="24" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="13" t="n">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>click</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>btn_dynamic_select</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>$data_login.select_hospital</t>
         </is>
       </c>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="24" t="n"/>
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="24" t="n"/>
+      <c r="L7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="13" t="n">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>check_status</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>lbl_dashboard_data</t>
         </is>
       </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>visible</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
+      <c r="I8" s="24" t="n"/>
+      <c r="J8" s="24" t="n"/>
+      <c r="K8" s="24" t="n"/>
+      <c r="L8" s="24" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>TC_LOGIN_002</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại với sai thông tin</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>neg</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>navigate</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>url_sit_login</t>
         </is>
       </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="24" t="n"/>
+      <c r="K9" s="24" t="n"/>
+      <c r="L9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="13" t="n">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>click</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>btn_sit_login</t>
         </is>
       </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="24" t="n"/>
+      <c r="K10" s="24" t="n"/>
+      <c r="L10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="13" t="n">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>txt_username</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>$data_login.username</t>
         </is>
       </c>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="24" t="n"/>
+      <c r="K11" s="24" t="n"/>
+      <c r="L11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="13" t="n">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>txt_password</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>$data_login.password</t>
         </is>
       </c>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="24" t="n"/>
+      <c r="K12" s="24" t="n"/>
+      <c r="L12" s="24" t="n"/>
     </row>
     <row r="13" ht="15.5" customHeight="1">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="13" t="n">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>click</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>btn_login</t>
         </is>
       </c>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="24" t="n"/>
+      <c r="L13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="13" t="n">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>check_status</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>error_msg</t>
         </is>
       </c>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>visible</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
+      <c r="I14" s="24" t="n"/>
+      <c r="J14" s="24" t="n"/>
+      <c r="K14" s="24" t="n"/>
+      <c r="L14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="n"/>
+      <c r="K15" s="24" t="n"/>
+      <c r="L15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="24" t="n"/>
+      <c r="K16" s="24" t="n"/>
+      <c r="L16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="24" t="n"/>
+      <c r="J17" s="24" t="n"/>
+      <c r="K17" s="24" t="n"/>
+      <c r="L17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="24" t="n"/>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="24" t="n"/>
+      <c r="L18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="24" t="n"/>
+      <c r="J19" s="24" t="n"/>
+      <c r="K19" s="24" t="n"/>
+      <c r="L19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="24" t="n"/>
+      <c r="J20" s="24" t="n"/>
+      <c r="K20" s="24" t="n"/>
+      <c r="L20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="14" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="24" t="n"/>
+      <c r="J21" s="24" t="n"/>
+      <c r="K21" s="24" t="n"/>
+      <c r="L21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="14" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="n"/>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="14" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="n"/>
+      <c r="K23" s="24" t="n"/>
+      <c r="L23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="23" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="24" t="n"/>
+      <c r="L24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="24" t="n"/>
+      <c r="J25" s="24" t="n"/>
+      <c r="K25" s="24" t="n"/>
+      <c r="L25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="n"/>
+      <c r="K26" s="24" t="n"/>
+      <c r="L26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="n"/>
+      <c r="K27" s="24" t="n"/>
+      <c r="L27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
+      <c r="A28" s="19" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="n"/>
+      <c r="K28" s="24" t="n"/>
+      <c r="L28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
+      <c r="A29" s="19" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="n"/>
+      <c r="K29" s="24" t="n"/>
+      <c r="L29" s="24" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="n"/>
+      <c r="K30" s="24" t="n"/>
+      <c r="L30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="21" t="n"/>
+      <c r="F31" s="21" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="24" t="n"/>
+      <c r="K31" s="24" t="n"/>
+      <c r="L31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
+      <c r="A32" s="19" t="n"/>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="21" t="n"/>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="24" t="n"/>
+      <c r="K32" s="24" t="n"/>
+      <c r="L32" s="24" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="24" t="n"/>
+      <c r="K33" s="24" t="n"/>
+      <c r="L33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
+      <c r="A34" s="19" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="21" t="n"/>
+      <c r="I34" s="24" t="n"/>
+      <c r="J34" s="24" t="n"/>
+      <c r="K34" s="24" t="n"/>
+      <c r="L34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="14" t="n"/>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
+      <c r="A35" s="19" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="21" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="21" t="n"/>
+      <c r="I35" s="24" t="n"/>
+      <c r="J35" s="24" t="n"/>
+      <c r="K35" s="24" t="n"/>
+      <c r="L35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
+      <c r="A36" s="19" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="24" t="n"/>
+      <c r="K36" s="24" t="n"/>
+      <c r="L36" s="24" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="14" t="n"/>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
+      <c r="A37" s="19" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="21" t="n"/>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="21" t="n"/>
+      <c r="I37" s="24" t="n"/>
+      <c r="J37" s="24" t="n"/>
+      <c r="K37" s="24" t="n"/>
+      <c r="L37" s="24" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="14" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="n"/>
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="23" t="n"/>
+      <c r="H38" s="21" t="n"/>
+      <c r="I38" s="24" t="n"/>
+      <c r="J38" s="24" t="n"/>
+      <c r="K38" s="24" t="n"/>
+      <c r="L38" s="24" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="14" t="n"/>
-      <c r="H39" s="12" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="21" t="n"/>
+      <c r="I39" s="24" t="n"/>
+      <c r="J39" s="24" t="n"/>
+      <c r="K39" s="24" t="n"/>
+      <c r="L39" s="24" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="14" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="23" t="n"/>
+      <c r="H40" s="21" t="n"/>
+      <c r="I40" s="24" t="n"/>
+      <c r="J40" s="24" t="n"/>
+      <c r="K40" s="24" t="n"/>
+      <c r="L40" s="24" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="14" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
+      <c r="A41" s="19" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="21" t="n"/>
+      <c r="I41" s="24" t="n"/>
+      <c r="J41" s="24" t="n"/>
+      <c r="K41" s="24" t="n"/>
+      <c r="L41" s="24" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="14" t="n"/>
-      <c r="H42" s="12" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="23" t="n"/>
+      <c r="H42" s="21" t="n"/>
+      <c r="I42" s="24" t="n"/>
+      <c r="J42" s="24" t="n"/>
+      <c r="K42" s="24" t="n"/>
+      <c r="L42" s="24" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="14" t="n"/>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
+      <c r="A43" s="19" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="21" t="n"/>
+      <c r="I43" s="24" t="n"/>
+      <c r="J43" s="24" t="n"/>
+      <c r="K43" s="24" t="n"/>
+      <c r="L43" s="24" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="14" t="n"/>
-      <c r="H44" s="12" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
+      <c r="A44" s="19" t="n"/>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="21" t="n"/>
+      <c r="I44" s="24" t="n"/>
+      <c r="J44" s="24" t="n"/>
+      <c r="K44" s="24" t="n"/>
+      <c r="L44" s="24" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="14" t="n"/>
-      <c r="H45" s="12" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
+      <c r="A45" s="19" t="n"/>
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="21" t="n"/>
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="24" t="n"/>
+      <c r="K45" s="24" t="n"/>
+      <c r="L45" s="24" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n"/>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="12" t="n"/>
-      <c r="G46" s="14" t="n"/>
-      <c r="H46" s="12" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
+      <c r="A46" s="19" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="23" t="n"/>
+      <c r="H46" s="21" t="n"/>
+      <c r="I46" s="24" t="n"/>
+      <c r="J46" s="24" t="n"/>
+      <c r="K46" s="24" t="n"/>
+      <c r="L46" s="24" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n"/>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="14" t="n"/>
-      <c r="H47" s="12" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
+      <c r="A47" s="19" t="n"/>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="21" t="n"/>
+      <c r="I47" s="24" t="n"/>
+      <c r="J47" s="24" t="n"/>
+      <c r="K47" s="24" t="n"/>
+      <c r="L47" s="24" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="n"/>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="12" t="n"/>
-      <c r="G48" s="14" t="n"/>
-      <c r="H48" s="12" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="5" t="n"/>
+      <c r="A48" s="19" t="n"/>
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="23" t="n"/>
+      <c r="H48" s="21" t="n"/>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="24" t="n"/>
+      <c r="K48" s="24" t="n"/>
+      <c r="L48" s="24" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="n"/>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="12" t="n"/>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="12" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
+      <c r="A49" s="19" t="n"/>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="23" t="n"/>
+      <c r="H49" s="21" t="n"/>
+      <c r="I49" s="24" t="n"/>
+      <c r="J49" s="24" t="n"/>
+      <c r="K49" s="24" t="n"/>
+      <c r="L49" s="24" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n"/>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="12" t="n"/>
-      <c r="G50" s="14" t="n"/>
-      <c r="H50" s="12" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="5" t="n"/>
+      <c r="A50" s="19" t="n"/>
+      <c r="B50" s="20" t="n"/>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="23" t="n"/>
+      <c r="H50" s="21" t="n"/>
+      <c r="I50" s="24" t="n"/>
+      <c r="J50" s="24" t="n"/>
+      <c r="K50" s="24" t="n"/>
+      <c r="L50" s="24" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n"/>
@@ -1592,6 +1685,496 @@
       <c r="K51" s="5" t="n"/>
       <c r="L51" s="5" t="n"/>
     </row>
+    <row r="52">
+      <c r="A52" s="27" t="n"/>
+      <c r="B52" s="27" t="n"/>
+      <c r="C52" s="27" t="n"/>
+      <c r="D52" s="27" t="n"/>
+      <c r="E52" s="27" t="n"/>
+      <c r="F52" s="27" t="n"/>
+      <c r="G52" s="27" t="n"/>
+      <c r="H52" s="27" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="27" t="n"/>
+      <c r="B53" s="27" t="n"/>
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="n"/>
+      <c r="F53" s="27" t="n"/>
+      <c r="G53" s="27" t="n"/>
+      <c r="H53" s="27" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="n"/>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="27" t="n"/>
+      <c r="H54" s="27" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="n"/>
+      <c r="B55" s="27" t="n"/>
+      <c r="C55" s="27" t="n"/>
+      <c r="D55" s="27" t="n"/>
+      <c r="E55" s="27" t="n"/>
+      <c r="F55" s="27" t="n"/>
+      <c r="G55" s="27" t="n"/>
+      <c r="H55" s="27" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="n"/>
+      <c r="B56" s="27" t="n"/>
+      <c r="C56" s="27" t="n"/>
+      <c r="D56" s="27" t="n"/>
+      <c r="E56" s="27" t="n"/>
+      <c r="F56" s="27" t="n"/>
+      <c r="G56" s="27" t="n"/>
+      <c r="H56" s="27" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="n"/>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="27" t="n"/>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
+      <c r="H57" s="27" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="n"/>
+      <c r="B58" s="27" t="n"/>
+      <c r="C58" s="27" t="n"/>
+      <c r="D58" s="27" t="n"/>
+      <c r="E58" s="27" t="n"/>
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="27" t="n"/>
+      <c r="H58" s="27" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="27" t="n"/>
+      <c r="B59" s="27" t="n"/>
+      <c r="C59" s="27" t="n"/>
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="27" t="n"/>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="27" t="n"/>
+      <c r="H59" s="27" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="27" t="n"/>
+      <c r="B60" s="27" t="n"/>
+      <c r="C60" s="27" t="n"/>
+      <c r="D60" s="27" t="n"/>
+      <c r="E60" s="27" t="n"/>
+      <c r="F60" s="27" t="n"/>
+      <c r="G60" s="27" t="n"/>
+      <c r="H60" s="27" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="27" t="n"/>
+      <c r="B61" s="27" t="n"/>
+      <c r="C61" s="27" t="n"/>
+      <c r="D61" s="27" t="n"/>
+      <c r="E61" s="27" t="n"/>
+      <c r="F61" s="27" t="n"/>
+      <c r="G61" s="27" t="n"/>
+      <c r="H61" s="27" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="27" t="n"/>
+      <c r="B62" s="27" t="n"/>
+      <c r="C62" s="27" t="n"/>
+      <c r="D62" s="27" t="n"/>
+      <c r="E62" s="27" t="n"/>
+      <c r="F62" s="27" t="n"/>
+      <c r="G62" s="27" t="n"/>
+      <c r="H62" s="27" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="27" t="n"/>
+      <c r="B63" s="27" t="n"/>
+      <c r="C63" s="27" t="n"/>
+      <c r="D63" s="27" t="n"/>
+      <c r="E63" s="27" t="n"/>
+      <c r="F63" s="27" t="n"/>
+      <c r="G63" s="27" t="n"/>
+      <c r="H63" s="27" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="n"/>
+      <c r="B64" s="27" t="n"/>
+      <c r="C64" s="27" t="n"/>
+      <c r="D64" s="27" t="n"/>
+      <c r="E64" s="27" t="n"/>
+      <c r="F64" s="27" t="n"/>
+      <c r="G64" s="27" t="n"/>
+      <c r="H64" s="27" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="n"/>
+      <c r="B65" s="27" t="n"/>
+      <c r="C65" s="27" t="n"/>
+      <c r="D65" s="27" t="n"/>
+      <c r="E65" s="27" t="n"/>
+      <c r="F65" s="27" t="n"/>
+      <c r="G65" s="27" t="n"/>
+      <c r="H65" s="27" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="n"/>
+      <c r="B66" s="27" t="n"/>
+      <c r="C66" s="27" t="n"/>
+      <c r="D66" s="27" t="n"/>
+      <c r="E66" s="27" t="n"/>
+      <c r="F66" s="27" t="n"/>
+      <c r="G66" s="27" t="n"/>
+      <c r="H66" s="27" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="27" t="n"/>
+      <c r="B67" s="27" t="n"/>
+      <c r="C67" s="27" t="n"/>
+      <c r="D67" s="27" t="n"/>
+      <c r="E67" s="27" t="n"/>
+      <c r="F67" s="27" t="n"/>
+      <c r="G67" s="27" t="n"/>
+      <c r="H67" s="27" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="27" t="n"/>
+      <c r="B68" s="27" t="n"/>
+      <c r="C68" s="27" t="n"/>
+      <c r="D68" s="27" t="n"/>
+      <c r="E68" s="27" t="n"/>
+      <c r="F68" s="27" t="n"/>
+      <c r="G68" s="27" t="n"/>
+      <c r="H68" s="27" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="27" t="n"/>
+      <c r="B69" s="27" t="n"/>
+      <c r="C69" s="27" t="n"/>
+      <c r="D69" s="27" t="n"/>
+      <c r="E69" s="27" t="n"/>
+      <c r="F69" s="27" t="n"/>
+      <c r="G69" s="27" t="n"/>
+      <c r="H69" s="27" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="n"/>
+      <c r="B70" s="27" t="n"/>
+      <c r="C70" s="27" t="n"/>
+      <c r="D70" s="27" t="n"/>
+      <c r="E70" s="27" t="n"/>
+      <c r="F70" s="27" t="n"/>
+      <c r="G70" s="27" t="n"/>
+      <c r="H70" s="27" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="n"/>
+      <c r="B71" s="27" t="n"/>
+      <c r="C71" s="27" t="n"/>
+      <c r="D71" s="27" t="n"/>
+      <c r="E71" s="27" t="n"/>
+      <c r="F71" s="27" t="n"/>
+      <c r="G71" s="27" t="n"/>
+      <c r="H71" s="27" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="n"/>
+      <c r="B72" s="27" t="n"/>
+      <c r="C72" s="27" t="n"/>
+      <c r="D72" s="27" t="n"/>
+      <c r="E72" s="27" t="n"/>
+      <c r="F72" s="27" t="n"/>
+      <c r="G72" s="27" t="n"/>
+      <c r="H72" s="27" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="n"/>
+      <c r="B73" s="27" t="n"/>
+      <c r="C73" s="27" t="n"/>
+      <c r="D73" s="27" t="n"/>
+      <c r="E73" s="27" t="n"/>
+      <c r="F73" s="27" t="n"/>
+      <c r="G73" s="27" t="n"/>
+      <c r="H73" s="27" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="n"/>
+      <c r="B74" s="27" t="n"/>
+      <c r="C74" s="27" t="n"/>
+      <c r="D74" s="27" t="n"/>
+      <c r="E74" s="27" t="n"/>
+      <c r="F74" s="27" t="n"/>
+      <c r="G74" s="27" t="n"/>
+      <c r="H74" s="27" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="n"/>
+      <c r="B75" s="27" t="n"/>
+      <c r="C75" s="27" t="n"/>
+      <c r="D75" s="27" t="n"/>
+      <c r="E75" s="27" t="n"/>
+      <c r="F75" s="27" t="n"/>
+      <c r="G75" s="27" t="n"/>
+      <c r="H75" s="27" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="27" t="n"/>
+      <c r="B76" s="27" t="n"/>
+      <c r="C76" s="27" t="n"/>
+      <c r="D76" s="27" t="n"/>
+      <c r="E76" s="27" t="n"/>
+      <c r="F76" s="27" t="n"/>
+      <c r="G76" s="27" t="n"/>
+      <c r="H76" s="27" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="27" t="n"/>
+      <c r="B77" s="27" t="n"/>
+      <c r="C77" s="27" t="n"/>
+      <c r="D77" s="27" t="n"/>
+      <c r="E77" s="27" t="n"/>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="27" t="n"/>
+      <c r="H77" s="27" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="27" t="n"/>
+      <c r="B78" s="27" t="n"/>
+      <c r="C78" s="27" t="n"/>
+      <c r="D78" s="27" t="n"/>
+      <c r="E78" s="27" t="n"/>
+      <c r="F78" s="27" t="n"/>
+      <c r="G78" s="27" t="n"/>
+      <c r="H78" s="27" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="27" t="n"/>
+      <c r="B79" s="27" t="n"/>
+      <c r="C79" s="27" t="n"/>
+      <c r="D79" s="27" t="n"/>
+      <c r="E79" s="27" t="n"/>
+      <c r="F79" s="27" t="n"/>
+      <c r="G79" s="27" t="n"/>
+      <c r="H79" s="27" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="27" t="n"/>
+      <c r="B80" s="27" t="n"/>
+      <c r="C80" s="27" t="n"/>
+      <c r="D80" s="27" t="n"/>
+      <c r="E80" s="27" t="n"/>
+      <c r="F80" s="27" t="n"/>
+      <c r="G80" s="27" t="n"/>
+      <c r="H80" s="27" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="27" t="n"/>
+      <c r="B81" s="27" t="n"/>
+      <c r="C81" s="27" t="n"/>
+      <c r="D81" s="27" t="n"/>
+      <c r="E81" s="27" t="n"/>
+      <c r="F81" s="27" t="n"/>
+      <c r="G81" s="27" t="n"/>
+      <c r="H81" s="27" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="27" t="n"/>
+      <c r="B82" s="27" t="n"/>
+      <c r="C82" s="27" t="n"/>
+      <c r="D82" s="27" t="n"/>
+      <c r="E82" s="27" t="n"/>
+      <c r="F82" s="27" t="n"/>
+      <c r="G82" s="27" t="n"/>
+      <c r="H82" s="27" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="27" t="n"/>
+      <c r="B83" s="27" t="n"/>
+      <c r="C83" s="27" t="n"/>
+      <c r="D83" s="27" t="n"/>
+      <c r="E83" s="27" t="n"/>
+      <c r="F83" s="27" t="n"/>
+      <c r="G83" s="27" t="n"/>
+      <c r="H83" s="27" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="27" t="n"/>
+      <c r="B84" s="27" t="n"/>
+      <c r="C84" s="27" t="n"/>
+      <c r="D84" s="27" t="n"/>
+      <c r="E84" s="27" t="n"/>
+      <c r="F84" s="27" t="n"/>
+      <c r="G84" s="27" t="n"/>
+      <c r="H84" s="27" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="27" t="n"/>
+      <c r="B85" s="27" t="n"/>
+      <c r="C85" s="27" t="n"/>
+      <c r="D85" s="27" t="n"/>
+      <c r="E85" s="27" t="n"/>
+      <c r="F85" s="27" t="n"/>
+      <c r="G85" s="27" t="n"/>
+      <c r="H85" s="27" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="n"/>
+      <c r="B86" s="27" t="n"/>
+      <c r="C86" s="27" t="n"/>
+      <c r="D86" s="27" t="n"/>
+      <c r="E86" s="27" t="n"/>
+      <c r="F86" s="27" t="n"/>
+      <c r="G86" s="27" t="n"/>
+      <c r="H86" s="27" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="27" t="n"/>
+      <c r="B87" s="27" t="n"/>
+      <c r="C87" s="27" t="n"/>
+      <c r="D87" s="27" t="n"/>
+      <c r="E87" s="27" t="n"/>
+      <c r="F87" s="27" t="n"/>
+      <c r="G87" s="27" t="n"/>
+      <c r="H87" s="27" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="27" t="n"/>
+      <c r="B88" s="27" t="n"/>
+      <c r="C88" s="27" t="n"/>
+      <c r="D88" s="27" t="n"/>
+      <c r="E88" s="27" t="n"/>
+      <c r="F88" s="27" t="n"/>
+      <c r="G88" s="27" t="n"/>
+      <c r="H88" s="27" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="27" t="n"/>
+      <c r="B89" s="27" t="n"/>
+      <c r="C89" s="27" t="n"/>
+      <c r="D89" s="27" t="n"/>
+      <c r="E89" s="27" t="n"/>
+      <c r="F89" s="27" t="n"/>
+      <c r="G89" s="27" t="n"/>
+      <c r="H89" s="27" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="27" t="n"/>
+      <c r="B90" s="27" t="n"/>
+      <c r="C90" s="27" t="n"/>
+      <c r="D90" s="27" t="n"/>
+      <c r="E90" s="27" t="n"/>
+      <c r="F90" s="27" t="n"/>
+      <c r="G90" s="27" t="n"/>
+      <c r="H90" s="27" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="27" t="n"/>
+      <c r="B91" s="27" t="n"/>
+      <c r="C91" s="27" t="n"/>
+      <c r="D91" s="27" t="n"/>
+      <c r="E91" s="27" t="n"/>
+      <c r="F91" s="27" t="n"/>
+      <c r="G91" s="27" t="n"/>
+      <c r="H91" s="27" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="27" t="n"/>
+      <c r="B92" s="27" t="n"/>
+      <c r="C92" s="27" t="n"/>
+      <c r="D92" s="27" t="n"/>
+      <c r="E92" s="27" t="n"/>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="27" t="n"/>
+      <c r="H92" s="27" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="n"/>
+      <c r="B93" s="27" t="n"/>
+      <c r="C93" s="27" t="n"/>
+      <c r="D93" s="27" t="n"/>
+      <c r="E93" s="27" t="n"/>
+      <c r="F93" s="27" t="n"/>
+      <c r="G93" s="27" t="n"/>
+      <c r="H93" s="27" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="27" t="n"/>
+      <c r="B94" s="27" t="n"/>
+      <c r="C94" s="27" t="n"/>
+      <c r="D94" s="27" t="n"/>
+      <c r="E94" s="27" t="n"/>
+      <c r="F94" s="27" t="n"/>
+      <c r="G94" s="27" t="n"/>
+      <c r="H94" s="27" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="27" t="n"/>
+      <c r="B95" s="27" t="n"/>
+      <c r="C95" s="27" t="n"/>
+      <c r="D95" s="27" t="n"/>
+      <c r="E95" s="27" t="n"/>
+      <c r="F95" s="27" t="n"/>
+      <c r="G95" s="27" t="n"/>
+      <c r="H95" s="27" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="27" t="n"/>
+      <c r="B96" s="27" t="n"/>
+      <c r="C96" s="27" t="n"/>
+      <c r="D96" s="27" t="n"/>
+      <c r="E96" s="27" t="n"/>
+      <c r="F96" s="27" t="n"/>
+      <c r="G96" s="27" t="n"/>
+      <c r="H96" s="27" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="27" t="n"/>
+      <c r="B97" s="27" t="n"/>
+      <c r="C97" s="27" t="n"/>
+      <c r="D97" s="27" t="n"/>
+      <c r="E97" s="27" t="n"/>
+      <c r="F97" s="27" t="n"/>
+      <c r="G97" s="27" t="n"/>
+      <c r="H97" s="27" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="27" t="n"/>
+      <c r="B98" s="27" t="n"/>
+      <c r="C98" s="27" t="n"/>
+      <c r="D98" s="27" t="n"/>
+      <c r="E98" s="27" t="n"/>
+      <c r="F98" s="27" t="n"/>
+      <c r="G98" s="27" t="n"/>
+      <c r="H98" s="27" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="27" t="n"/>
+      <c r="B99" s="27" t="n"/>
+      <c r="C99" s="27" t="n"/>
+      <c r="D99" s="27" t="n"/>
+      <c r="E99" s="27" t="n"/>
+      <c r="F99" s="27" t="n"/>
+      <c r="G99" s="27" t="n"/>
+      <c r="H99" s="27" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="27" t="n"/>
+      <c r="B100" s="27" t="n"/>
+      <c r="C100" s="27" t="n"/>
+      <c r="D100" s="27" t="n"/>
+      <c r="E100" s="27" t="n"/>
+      <c r="F100" s="27" t="n"/>
+      <c r="G100" s="27" t="n"/>
+      <c r="H100" s="27" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1" password="CF7A"/>
   <conditionalFormatting sqref="J2:J51">
@@ -1602,6 +2185,25 @@
       <formula>"Failed"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J100">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="5">
+      <formula>"Passed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="6">
+      <formula>"Failed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dữ liệu không hợp lệ" error="Vui lòng chọn 'pos' hoặc 'neg'." type="list" errorStyle="stop">
+      <formula1>"pos,neg"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dữ liệu không hợp lệ" error="Vui lòng chọn đúng action từ danh sách ACTION_LIST." type="list" errorStyle="stop">
+      <formula1>OFFSET(ACTION_LIST!$A$2,0,0,COUNTA(ACTION_LIST!$A:$A)-1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dữ liệu không hợp lệ" error="Vui lòng chọn đúng target từ danh sách element_id của sheet ELEMENT." type="list" errorStyle="stop">
+      <formula1>OFFSET(ELEMENT!$A$2,0,0,COUNTA(ELEMENT!$A:$A)-1,1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
@@ -1621,12 +2223,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>page</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>url</t>
         </is>
@@ -1671,6 +2273,9 @@
   </sheetData>
   <conditionalFormatting sqref="A2:A100">
     <cfRule type="expression" priority="1" dxfId="0">
+      <formula>COUNTIF($A$2:$A$100,A2)&gt;1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="6">
       <formula>COUNTIF($A$2:$A$100,A2)&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1696,17 +2301,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>element_id</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>locator_type</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>locator_value</t>
         </is>
@@ -1961,9 +2566,14 @@
       <formula>COUNTIF($A$2:$A$1000,A15)&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A1000">
+    <cfRule type="expression" priority="3" dxfId="6">
+      <formula>COUNTIF($A$2:$A$1000,A2)&gt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"css,xpath,id,name,PAGE"</formula1>
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dữ liệu không hợp lệ" error="Vui lòng chọn đúng locator type từ danh sách." type="list" errorStyle="stop">
+      <formula1>"css,xpath,id,name,page"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1987,37 +2597,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>test_case_type</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>username</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="28" t="inlineStr">
         <is>
           <t>select_hospital</t>
         </is>
       </c>
-      <c r="E1" s="6" t="n"/>
-      <c r="F1" s="6" t="n"/>
-      <c r="G1" s="6" t="n"/>
-      <c r="H1" s="6" t="n"/>
-      <c r="I1" s="6" t="n"/>
-      <c r="J1" s="6" t="n"/>
-      <c r="K1" s="6" t="n"/>
-      <c r="L1" s="6" t="n"/>
-      <c r="M1" s="6" t="n"/>
-      <c r="N1" s="6" t="n"/>
-      <c r="O1" s="6" t="n"/>
+      <c r="E1" s="28" t="n"/>
+      <c r="F1" s="28" t="n"/>
+      <c r="G1" s="28" t="n"/>
+      <c r="H1" s="28" t="n"/>
+      <c r="I1" s="28" t="n"/>
+      <c r="J1" s="28" t="n"/>
+      <c r="K1" s="28" t="n"/>
+      <c r="L1" s="28" t="n"/>
+      <c r="M1" s="28" t="n"/>
+      <c r="N1" s="28" t="n"/>
+      <c r="O1" s="28" t="n"/>
     </row>
     <row r="2" ht="15.5" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -2067,7 +2677,7 @@
     <row r="10" ht="15.5" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dữ liệu không hợp lệ" error="Vui lòng chọn 'pos' hoặc 'neg'." type="list" errorStyle="stop">
       <formula1>"pos,neg"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2094,324 +2704,324 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>navigate</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>Mở URL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>go_back</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Quay lại trang trước</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>go_forward</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Tiến tới trang tiếp theo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>refresh</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Reload trang hiện tại</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>check_status</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Kiểm tra trạng thái element theo expect (visible, exists, text, value, enabled, checked…)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>click</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Click vào element</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>double_click</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Double click vào element</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>right_click</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Click chuột phải vào element</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>hover</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Di chuột lên element</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>focus</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Focus vào element</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>blur</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Rời focus khỏi element</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>press_key</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Nhấn phím (Enter, Tab, Esc…)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Nhập text vào field</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>clear</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>Xóa text trong field</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>upload_file</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>Upload file qua input type=file</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>drag_drop</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>Kéo thả element tới target</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>scroll_to</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Scroll tới element</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>scroll_by</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>Scroll theo tọa độ (x, y)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>select_by_text</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>Chọn dropdown theo text hiển thị</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>select_by_value</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>Chọn dropdown theo value</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>Check checkbox</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>uncheck</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>Uncheck checkbox</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>screenshot</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>Chụp màn hình</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>log</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>Ghi log message</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>fail</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Force fail test</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>Skip step hoặc test case</t>
         </is>

--- a/test-data/Template_Master_Test_Suite.xlsx
+++ b/test-data/Template_Master_Test_Suite.xlsx
@@ -7,24 +7,24 @@
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="6" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="156" name="PAGE" state="visible" r:id="rId4"/>
-    <sheet sheetId="157" name="ACTION_LIST" state="visible" r:id="rId5"/>
-    <sheet sheetId="158" name="TEST_CASE_LOGIN" state="visible" r:id="rId6"/>
-    <sheet sheetId="159" name="DATA_LOGIN" state="visible" r:id="rId7"/>
-    <sheet sheetId="160" name="ELEMENT_LOGIN" state="visible" r:id="rId8"/>
-    <sheet sheetId="161" name="TEST_CASE_VACXIN" state="visible" r:id="rId9"/>
-    <sheet sheetId="162" name="DATA_VACXIN" state="visible" r:id="rId10"/>
-    <sheet sheetId="163" name="ELEMENT_VACXIN" state="visible" r:id="rId11"/>
-    <sheet sheetId="164" name="TEST_CASE_QLHV" state="visible" r:id="rId12"/>
-    <sheet sheetId="165" name="DATA_QLHV" state="visible" r:id="rId13"/>
-    <sheet sheetId="166" name="ELEMENT_QLHV" state="visible" r:id="rId14"/>
+    <sheet name="PAGE" sheetId="180" r:id="rId28"/>
+    <sheet name="ACTION_LIST" sheetId="181" r:id="rId29"/>
+    <sheet name="TEST_CASE_LOGIN" sheetId="182" r:id="rId30"/>
+    <sheet name="DATA_LOGIN" sheetId="183" r:id="rId31"/>
+    <sheet name="ELEMENT_LOGIN" sheetId="184" r:id="rId32"/>
+    <sheet name="TEST_CASE_VACXIN" sheetId="185" r:id="rId33"/>
+    <sheet name="DATA_VACXIN" sheetId="186" r:id="rId34"/>
+    <sheet name="ELEMENT_VACXIN" sheetId="187" r:id="rId35"/>
+    <sheet name="TEST_CASE_QLHV" sheetId="188" r:id="rId36"/>
+    <sheet name="DATA_QLHV" sheetId="189" r:id="rId37"/>
+    <sheet name="ELEMENT_QLHV" sheetId="190" r:id="rId38"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>page</t>
   </si>
@@ -987,13 +987,314 @@
   </si>
   <si>
     <t>//*[contains(text(), 'Ghép cặp thành công') or contains(text(), 'Thành công')]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ds_ep_email_neg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ds_bva_phone_neg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ds_bva_cccd_neg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ds_decision_table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_QLHV_PRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precondition: Đăng nhập thành công và đi tới trang Quản lý học viên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thêm học viên mới thành công (Đầy đủ thông tin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_job_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbl_toast_success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_QLHV_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thêm học viên mới thất bại (Để trống trường bắt buộc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbl_toast_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_QLHV_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivalence Partitioning: Kiểm tra Email sai định dạng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_QLHV_004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundary Value Analysis: Kiểm tra Số điện thoại sai độ dài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_QLHV_005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundary Value Analysis: Kiểm tra CCCD sai độ dài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_QLHV_006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision Table Testing: Phân loại học viên vs Mã nhân viên bắt buộc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$data_qlhv.expected_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$data_qlhv.expected_success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expected_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expected_success</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">An Toàn người bệnh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Học mổ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn EP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lớp học xóa mù SMH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.student@</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@vinmec.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn BVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">098765432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09876543210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09876543ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn CCCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00109501234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0010950123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nội bộ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- MÀN HÌNH ĐẠO TẠO LÂM SÀNG - ĐIỀU HƯỚNG ---</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data-testid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-add-button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-employee-id-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-name-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-dob-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-cccd-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-gender-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-profession-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-position-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-job-title-other-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-degree-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_specialty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-specialty-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_workplace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-hospital-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-department-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-email-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-phone-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label:has-text("${data}")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-tax-code-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-bank-account-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-bank-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-program-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-class-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_mentor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-mentor-select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-university-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-start-date-input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-submit-button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btn_trainee_cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training-trainees-upsert-cancel-button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[role="option"]:has-text("${data}")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[data-sonner-toast][data-type='success']</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[data-sonner-toast][data-type='error']</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbl_validation_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.text-destructive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">button[name="Xác nhận ghép cặp"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghép cặp thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddl_trainee_role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision Table Testing: Phân loại học viên vs Mã nhân viên bắt buộc (Positive)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dt_pos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_QLHV_007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision Table Testing: Phân loại học viên vs Mã nhân viên bắt buộc (Negative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dt_neg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">span:has-text("13.4 Điều phối")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a[href*="mentor-matching"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a[href*="clinical-logbook"]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts/>
+  <fonts x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1005,8 +1306,688 @@
       <b/>
       <color rgb="FFFFFF"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills>
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1018,8 +1999,2048 @@
         <fgColor rgb="1A3A4A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A3A4A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1031,13 +4052,523 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="5" fillId="6" borderId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="6" fillId="7" borderId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="7" fillId="8" borderId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="8" fillId="9" borderId="7" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="8" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="10" fillId="11" borderId="9" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="11" fillId="12" borderId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="12" fillId="13" borderId="11" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="13" fillId="14" borderId="12" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="14" fillId="15" borderId="13" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="15" fillId="16" borderId="14" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="16" fillId="17" borderId="15" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="17" fillId="18" borderId="16" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="18" fillId="19" borderId="17" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="19" fillId="20" borderId="18" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="20" fillId="21" borderId="19" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="21" fillId="22" borderId="20" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="22" fillId="23" borderId="21" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="23" fillId="24" borderId="22" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="24" fillId="25" borderId="23" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="25" fillId="26" borderId="24" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="26" fillId="27" borderId="25" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="27" fillId="28" borderId="26" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="28" fillId="29" borderId="27" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="29" fillId="30" borderId="28" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="30" fillId="31" borderId="29" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="31" fillId="32" borderId="30" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="32" fillId="33" borderId="31" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="33" fillId="34" borderId="32" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="34" fillId="35" borderId="33" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="35" fillId="36" borderId="34" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="36" fillId="37" borderId="35" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="37" fillId="38" borderId="36" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="38" fillId="39" borderId="37" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="39" fillId="40" borderId="38" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="40" fillId="41" borderId="39" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="41" fillId="42" borderId="40" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="42" fillId="43" borderId="41" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="43" fillId="44" borderId="42" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="44" fillId="45" borderId="43" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="45" fillId="46" borderId="44" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="46" fillId="47" borderId="45" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="47" fillId="48" borderId="46" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="48" fillId="49" borderId="47" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="49" fillId="50" borderId="48" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="50" fillId="51" borderId="49" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="51" fillId="52" borderId="50" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="52" fillId="53" borderId="51" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="53" fillId="54" borderId="52" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="54" fillId="55" borderId="53" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="55" fillId="56" borderId="54" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="56" fillId="57" borderId="55" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="57" fillId="58" borderId="56" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="58" fillId="59" borderId="57" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="59" fillId="60" borderId="58" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="60" fillId="61" borderId="59" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="61" fillId="62" borderId="60" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="62" fillId="63" borderId="61" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="63" fillId="64" borderId="62" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="64" fillId="65" borderId="63" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="65" fillId="66" borderId="64" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="66" fillId="67" borderId="65" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="67" fillId="68" borderId="66" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="68" fillId="69" borderId="67" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="69" fillId="70" borderId="68" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="70" fillId="71" borderId="69" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="71" fillId="72" borderId="70" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="72" fillId="73" borderId="71" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="73" fillId="74" borderId="72" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="74" fillId="75" borderId="73" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="75" fillId="76" borderId="74" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="76" fillId="77" borderId="75" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="77" fillId="78" borderId="76" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="78" fillId="79" borderId="77" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="79" fillId="80" borderId="78" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="80" fillId="81" borderId="79" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="81" fillId="82" borderId="80" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="82" fillId="83" borderId="81" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="83" fillId="84" borderId="82" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="84" fillId="85" borderId="83" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="85" fillId="86" borderId="84" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="86" fillId="87" borderId="85" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="87" fillId="88" borderId="86" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="88" fillId="89" borderId="87" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="89" fillId="90" borderId="88" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="90" fillId="91" borderId="89" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="91" fillId="92" borderId="90" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="92" fillId="93" borderId="91" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="93" fillId="94" borderId="92" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="94" fillId="95" borderId="93" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="95" fillId="96" borderId="94" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="96" fillId="97" borderId="95" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="97" fillId="98" borderId="96" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="98" fillId="99" borderId="97" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="99" fillId="100" borderId="98" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="100" fillId="101" borderId="99" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="101" fillId="102" borderId="100" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="102" fillId="103" borderId="101" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="103" fillId="104" borderId="102" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="104" fillId="105" borderId="103" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="105" fillId="106" borderId="104" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="106" fillId="107" borderId="105" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="107" fillId="108" borderId="106" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="108" fillId="109" borderId="107" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="109" fillId="110" borderId="108" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="110" fillId="111" borderId="109" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="111" fillId="112" borderId="110" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="112" fillId="113" borderId="111" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="113" fillId="114" borderId="112" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="114" fillId="115" borderId="113" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="115" fillId="116" borderId="114" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="116" fillId="117" borderId="115" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="117" fillId="118" borderId="116" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="118" fillId="119" borderId="117" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="119" fillId="120" borderId="118" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="120" fillId="121" borderId="119" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="121" fillId="122" borderId="120" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="122" fillId="123" borderId="121" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="123" fillId="124" borderId="122" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="124" fillId="125" borderId="123" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="125" fillId="126" borderId="124" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="126" fillId="127" borderId="125" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="127" fillId="128" borderId="126" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="128" fillId="129" borderId="127" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="129" fillId="130" borderId="128" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="130" fillId="131" borderId="129" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="131" fillId="132" borderId="130" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="132" fillId="133" borderId="131" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="133" fillId="134" borderId="132" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="134" fillId="135" borderId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="135" fillId="136" borderId="134" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="136" fillId="137" borderId="135" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="137" fillId="138" borderId="136" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="138" fillId="139" borderId="137" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="139" fillId="140" borderId="138" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="140" fillId="141" borderId="139" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="141" fillId="142" borderId="140" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="142" fillId="143" borderId="141" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="143" fillId="144" borderId="142" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="144" fillId="145" borderId="143" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="145" fillId="146" borderId="144" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="146" fillId="147" borderId="145" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="147" fillId="148" borderId="146" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="148" fillId="149" borderId="147" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="149" fillId="150" borderId="148" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="150" fillId="151" borderId="149" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="151" fillId="152" borderId="150" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="152" fillId="153" borderId="151" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="153" fillId="154" borderId="152" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="154" fillId="155" borderId="153" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="155" fillId="156" borderId="154" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="156" fillId="157" borderId="155" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="157" fillId="158" borderId="156" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="158" fillId="159" borderId="157" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="159" fillId="160" borderId="158" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="160" fillId="161" borderId="159" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="161" fillId="162" borderId="160" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="162" fillId="163" borderId="161" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="163" fillId="164" borderId="162" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="164" fillId="165" borderId="163" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="165" fillId="166" borderId="164" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="166" fillId="167" borderId="165" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="167" fillId="168" borderId="166" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="168" fillId="169" borderId="167" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="169" fillId="170" borderId="168" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="170" fillId="171" borderId="169" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="171" fillId="172" borderId="170" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1376,6 +4907,1524 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="88">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="144">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s" s="145">
+        <v>233</v>
+      </c>
+      <c r="C1" t="s" s="146">
+        <v>234</v>
+      </c>
+      <c r="D1" t="s" s="147">
+        <v>235</v>
+      </c>
+      <c r="E1" t="s" s="148">
+        <v>236</v>
+      </c>
+      <c r="F1" t="s" s="149">
+        <v>237</v>
+      </c>
+      <c r="G1" t="s" s="150">
+        <v>238</v>
+      </c>
+      <c r="H1" t="s" s="151">
+        <v>239</v>
+      </c>
+      <c r="I1" t="s" s="152">
+        <v>240</v>
+      </c>
+      <c r="J1" t="s" s="153">
+        <v>241</v>
+      </c>
+      <c r="K1" t="s" s="154">
+        <v>242</v>
+      </c>
+      <c r="L1" t="s" s="155">
+        <v>243</v>
+      </c>
+      <c r="M1" t="s" s="156">
+        <v>244</v>
+      </c>
+      <c r="N1" t="s" s="157">
+        <v>245</v>
+      </c>
+      <c r="O1" t="s" s="158">
+        <v>246</v>
+      </c>
+      <c r="P1" t="s" s="159">
+        <v>247</v>
+      </c>
+      <c r="Q1" t="s" s="160">
+        <v>248</v>
+      </c>
+      <c r="R1" t="s" s="161">
+        <v>249</v>
+      </c>
+      <c r="S1" t="s" s="162">
+        <v>250</v>
+      </c>
+      <c r="T1" t="s" s="163">
+        <v>251</v>
+      </c>
+      <c r="U1" t="s" s="164">
+        <v>252</v>
+      </c>
+      <c r="V1" t="s" s="165">
+        <v>253</v>
+      </c>
+      <c r="W1" t="s" s="166">
+        <v>254</v>
+      </c>
+      <c r="X1" t="s" s="167">
+        <v>255</v>
+      </c>
+      <c r="Y1" t="s" s="168">
+        <v>345</v>
+      </c>
+      <c r="Z1" t="s" s="169">
+        <v>346</v>
+      </c>
+      <c r="AA1"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I2" t="s">
+        <v>417</v>
+      </c>
+      <c r="J2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M2" t="s">
+        <v>266</v>
+      </c>
+      <c r="N2" t="s">
+        <v>267</v>
+      </c>
+      <c r="O2" t="s">
+        <v>268</v>
+      </c>
+      <c r="P2" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>270</v>
+      </c>
+      <c r="R2" t="s">
+        <v>271</v>
+      </c>
+      <c r="S2" t="s">
+        <v>272</v>
+      </c>
+      <c r="T2" t="s">
+        <v>348</v>
+      </c>
+      <c r="U2" t="s">
+        <v>349</v>
+      </c>
+      <c r="V2" t="s">
+        <v>275</v>
+      </c>
+      <c r="W2" t="s">
+        <v>276</v>
+      </c>
+      <c r="X2" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I3" t="s">
+        <v>417</v>
+      </c>
+      <c r="J3" t="s">
+        <v>283</v>
+      </c>
+      <c r="K3" t="s">
+        <v>264</v>
+      </c>
+      <c r="L3" t="s">
+        <v>265</v>
+      </c>
+      <c r="M3" t="s">
+        <v>266</v>
+      </c>
+      <c r="N3" t="s">
+        <v>284</v>
+      </c>
+      <c r="O3" t="s">
+        <v>285</v>
+      </c>
+      <c r="P3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>417</v>
+      </c>
+      <c r="R3" t="s">
+        <v>417</v>
+      </c>
+      <c r="S3" t="s">
+        <v>417</v>
+      </c>
+      <c r="T3" t="s">
+        <v>417</v>
+      </c>
+      <c r="U3" t="s">
+        <v>417</v>
+      </c>
+      <c r="V3" t="s">
+        <v>417</v>
+      </c>
+      <c r="W3" t="s">
+        <v>417</v>
+      </c>
+      <c r="X3" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" t="s">
+        <v>417</v>
+      </c>
+      <c r="F4" t="s">
+        <v>417</v>
+      </c>
+      <c r="G4" t="s">
+        <v>261</v>
+      </c>
+      <c r="H4" t="s">
+        <v>417</v>
+      </c>
+      <c r="I4" t="s">
+        <v>417</v>
+      </c>
+      <c r="J4" t="s">
+        <v>417</v>
+      </c>
+      <c r="K4" t="s">
+        <v>417</v>
+      </c>
+      <c r="L4" t="s">
+        <v>417</v>
+      </c>
+      <c r="M4" t="s">
+        <v>417</v>
+      </c>
+      <c r="N4" t="s">
+        <v>351</v>
+      </c>
+      <c r="O4" t="s">
+        <v>268</v>
+      </c>
+      <c r="P4" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>417</v>
+      </c>
+      <c r="R4" t="s">
+        <v>417</v>
+      </c>
+      <c r="S4" t="s">
+        <v>417</v>
+      </c>
+      <c r="T4" t="s">
+        <v>348</v>
+      </c>
+      <c r="U4" t="s">
+        <v>352</v>
+      </c>
+      <c r="V4" t="s">
+        <v>417</v>
+      </c>
+      <c r="W4" t="s">
+        <v>417</v>
+      </c>
+      <c r="X4" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" t="s">
+        <v>258</v>
+      </c>
+      <c r="E5" t="s">
+        <v>417</v>
+      </c>
+      <c r="F5" t="s">
+        <v>417</v>
+      </c>
+      <c r="G5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H5" t="s">
+        <v>417</v>
+      </c>
+      <c r="I5" t="s">
+        <v>417</v>
+      </c>
+      <c r="J5" t="s">
+        <v>417</v>
+      </c>
+      <c r="K5" t="s">
+        <v>417</v>
+      </c>
+      <c r="L5" t="s">
+        <v>417</v>
+      </c>
+      <c r="M5" t="s">
+        <v>417</v>
+      </c>
+      <c r="N5" t="s">
+        <v>353</v>
+      </c>
+      <c r="O5" t="s">
+        <v>268</v>
+      </c>
+      <c r="P5" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>417</v>
+      </c>
+      <c r="R5" t="s">
+        <v>417</v>
+      </c>
+      <c r="S5" t="s">
+        <v>417</v>
+      </c>
+      <c r="T5" t="s">
+        <v>348</v>
+      </c>
+      <c r="U5" t="s">
+        <v>352</v>
+      </c>
+      <c r="V5" t="s">
+        <v>417</v>
+      </c>
+      <c r="W5" t="s">
+        <v>417</v>
+      </c>
+      <c r="X5" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" t="s">
+        <v>417</v>
+      </c>
+      <c r="F6" t="s">
+        <v>417</v>
+      </c>
+      <c r="G6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H6" t="s">
+        <v>417</v>
+      </c>
+      <c r="I6" t="s">
+        <v>417</v>
+      </c>
+      <c r="J6" t="s">
+        <v>417</v>
+      </c>
+      <c r="K6" t="s">
+        <v>417</v>
+      </c>
+      <c r="L6" t="s">
+        <v>417</v>
+      </c>
+      <c r="M6" t="s">
+        <v>417</v>
+      </c>
+      <c r="N6" t="s">
+        <v>354</v>
+      </c>
+      <c r="O6" t="s">
+        <v>268</v>
+      </c>
+      <c r="P6" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>417</v>
+      </c>
+      <c r="R6" t="s">
+        <v>417</v>
+      </c>
+      <c r="S6" t="s">
+        <v>417</v>
+      </c>
+      <c r="T6" t="s">
+        <v>348</v>
+      </c>
+      <c r="U6" t="s">
+        <v>352</v>
+      </c>
+      <c r="V6" t="s">
+        <v>417</v>
+      </c>
+      <c r="W6" t="s">
+        <v>417</v>
+      </c>
+      <c r="X6" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E7" t="s">
+        <v>417</v>
+      </c>
+      <c r="F7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H7" t="s">
+        <v>417</v>
+      </c>
+      <c r="I7" t="s">
+        <v>417</v>
+      </c>
+      <c r="J7" t="s">
+        <v>417</v>
+      </c>
+      <c r="K7" t="s">
+        <v>417</v>
+      </c>
+      <c r="L7" t="s">
+        <v>417</v>
+      </c>
+      <c r="M7" t="s">
+        <v>417</v>
+      </c>
+      <c r="N7" t="s">
+        <v>267</v>
+      </c>
+      <c r="O7" t="s">
+        <v>356</v>
+      </c>
+      <c r="P7" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>417</v>
+      </c>
+      <c r="R7" t="s">
+        <v>417</v>
+      </c>
+      <c r="S7" t="s">
+        <v>417</v>
+      </c>
+      <c r="T7" t="s">
+        <v>348</v>
+      </c>
+      <c r="U7" t="s">
+        <v>352</v>
+      </c>
+      <c r="V7" t="s">
+        <v>417</v>
+      </c>
+      <c r="W7" t="s">
+        <v>417</v>
+      </c>
+      <c r="X7" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" t="s">
+        <v>417</v>
+      </c>
+      <c r="F8" t="s">
+        <v>417</v>
+      </c>
+      <c r="G8" t="s">
+        <v>261</v>
+      </c>
+      <c r="H8" t="s">
+        <v>417</v>
+      </c>
+      <c r="I8" t="s">
+        <v>417</v>
+      </c>
+      <c r="J8" t="s">
+        <v>417</v>
+      </c>
+      <c r="K8" t="s">
+        <v>417</v>
+      </c>
+      <c r="L8" t="s">
+        <v>417</v>
+      </c>
+      <c r="M8" t="s">
+        <v>417</v>
+      </c>
+      <c r="N8" t="s">
+        <v>267</v>
+      </c>
+      <c r="O8" t="s">
+        <v>357</v>
+      </c>
+      <c r="P8" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>417</v>
+      </c>
+      <c r="R8" t="s">
+        <v>417</v>
+      </c>
+      <c r="S8" t="s">
+        <v>417</v>
+      </c>
+      <c r="T8" t="s">
+        <v>348</v>
+      </c>
+      <c r="U8" t="s">
+        <v>352</v>
+      </c>
+      <c r="V8" t="s">
+        <v>417</v>
+      </c>
+      <c r="W8" t="s">
+        <v>417</v>
+      </c>
+      <c r="X8" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9" t="s">
+        <v>355</v>
+      </c>
+      <c r="D9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E9" t="s">
+        <v>417</v>
+      </c>
+      <c r="F9" t="s">
+        <v>417</v>
+      </c>
+      <c r="G9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H9" t="s">
+        <v>417</v>
+      </c>
+      <c r="I9" t="s">
+        <v>417</v>
+      </c>
+      <c r="J9" t="s">
+        <v>417</v>
+      </c>
+      <c r="K9" t="s">
+        <v>417</v>
+      </c>
+      <c r="L9" t="s">
+        <v>417</v>
+      </c>
+      <c r="M9" t="s">
+        <v>417</v>
+      </c>
+      <c r="N9" t="s">
+        <v>267</v>
+      </c>
+      <c r="O9" t="s">
+        <v>358</v>
+      </c>
+      <c r="P9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>417</v>
+      </c>
+      <c r="R9" t="s">
+        <v>417</v>
+      </c>
+      <c r="S9" t="s">
+        <v>417</v>
+      </c>
+      <c r="T9" t="s">
+        <v>348</v>
+      </c>
+      <c r="U9" t="s">
+        <v>352</v>
+      </c>
+      <c r="V9" t="s">
+        <v>417</v>
+      </c>
+      <c r="W9" t="s">
+        <v>417</v>
+      </c>
+      <c r="X9" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>323</v>
+      </c>
+      <c r="B10" t="s">
+        <v>417</v>
+      </c>
+      <c r="C10" t="s">
+        <v>359</v>
+      </c>
+      <c r="D10" t="s">
+        <v>258</v>
+      </c>
+      <c r="E10" t="s">
+        <v>360</v>
+      </c>
+      <c r="F10" t="s">
+        <v>417</v>
+      </c>
+      <c r="G10" t="s">
+        <v>261</v>
+      </c>
+      <c r="H10" t="s">
+        <v>417</v>
+      </c>
+      <c r="I10" t="s">
+        <v>417</v>
+      </c>
+      <c r="J10" t="s">
+        <v>417</v>
+      </c>
+      <c r="K10" t="s">
+        <v>417</v>
+      </c>
+      <c r="L10" t="s">
+        <v>417</v>
+      </c>
+      <c r="M10" t="s">
+        <v>417</v>
+      </c>
+      <c r="N10" t="s">
+        <v>267</v>
+      </c>
+      <c r="O10" t="s">
+        <v>268</v>
+      </c>
+      <c r="P10" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>417</v>
+      </c>
+      <c r="R10" t="s">
+        <v>417</v>
+      </c>
+      <c r="S10" t="s">
+        <v>417</v>
+      </c>
+      <c r="T10" t="s">
+        <v>348</v>
+      </c>
+      <c r="U10" t="s">
+        <v>352</v>
+      </c>
+      <c r="V10" t="s">
+        <v>417</v>
+      </c>
+      <c r="W10" t="s">
+        <v>417</v>
+      </c>
+      <c r="X10" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B11" t="s">
+        <v>417</v>
+      </c>
+      <c r="C11" t="s">
+        <v>359</v>
+      </c>
+      <c r="D11" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" t="s">
+        <v>361</v>
+      </c>
+      <c r="F11" t="s">
+        <v>417</v>
+      </c>
+      <c r="G11" t="s">
+        <v>261</v>
+      </c>
+      <c r="H11" t="s">
+        <v>417</v>
+      </c>
+      <c r="I11" t="s">
+        <v>417</v>
+      </c>
+      <c r="J11" t="s">
+        <v>417</v>
+      </c>
+      <c r="K11" t="s">
+        <v>417</v>
+      </c>
+      <c r="L11" t="s">
+        <v>417</v>
+      </c>
+      <c r="M11" t="s">
+        <v>417</v>
+      </c>
+      <c r="N11" t="s">
+        <v>267</v>
+      </c>
+      <c r="O11" t="s">
+        <v>268</v>
+      </c>
+      <c r="P11" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>417</v>
+      </c>
+      <c r="R11" t="s">
+        <v>417</v>
+      </c>
+      <c r="S11" t="s">
+        <v>417</v>
+      </c>
+      <c r="T11" t="s">
+        <v>348</v>
+      </c>
+      <c r="U11" t="s">
+        <v>352</v>
+      </c>
+      <c r="V11" t="s">
+        <v>417</v>
+      </c>
+      <c r="W11" t="s">
+        <v>417</v>
+      </c>
+      <c r="X11" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B12" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E12" t="s">
+        <v>417</v>
+      </c>
+      <c r="F12" t="s">
+        <v>417</v>
+      </c>
+      <c r="G12" t="s">
+        <v>261</v>
+      </c>
+      <c r="H12" t="s">
+        <v>417</v>
+      </c>
+      <c r="I12" t="s">
+        <v>417</v>
+      </c>
+      <c r="J12" t="s">
+        <v>417</v>
+      </c>
+      <c r="K12" t="s">
+        <v>417</v>
+      </c>
+      <c r="L12" t="s">
+        <v>417</v>
+      </c>
+      <c r="M12" t="s">
+        <v>417</v>
+      </c>
+      <c r="N12" t="s">
+        <v>267</v>
+      </c>
+      <c r="O12" t="s">
+        <v>268</v>
+      </c>
+      <c r="P12" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>417</v>
+      </c>
+      <c r="R12" t="s">
+        <v>417</v>
+      </c>
+      <c r="S12" t="s">
+        <v>417</v>
+      </c>
+      <c r="T12" t="s">
+        <v>348</v>
+      </c>
+      <c r="U12" t="s">
+        <v>349</v>
+      </c>
+      <c r="V12" t="s">
+        <v>417</v>
+      </c>
+      <c r="W12" t="s">
+        <v>417</v>
+      </c>
+      <c r="X12" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>416</v>
+      </c>
+      <c r="B13" t="s">
+        <v>417</v>
+      </c>
+      <c r="C13" t="s">
+        <v>362</v>
+      </c>
+      <c r="D13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E13" t="s">
+        <v>417</v>
+      </c>
+      <c r="F13" t="s">
+        <v>417</v>
+      </c>
+      <c r="G13" t="s">
+        <v>261</v>
+      </c>
+      <c r="H13" t="s">
+        <v>417</v>
+      </c>
+      <c r="I13" t="s">
+        <v>417</v>
+      </c>
+      <c r="J13" t="s">
+        <v>417</v>
+      </c>
+      <c r="K13" t="s">
+        <v>417</v>
+      </c>
+      <c r="L13" t="s">
+        <v>417</v>
+      </c>
+      <c r="M13" t="s">
+        <v>417</v>
+      </c>
+      <c r="N13" t="s">
+        <v>267</v>
+      </c>
+      <c r="O13" t="s">
+        <v>268</v>
+      </c>
+      <c r="P13" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>417</v>
+      </c>
+      <c r="R13" t="s">
+        <v>417</v>
+      </c>
+      <c r="S13" t="s">
+        <v>417</v>
+      </c>
+      <c r="T13" t="s">
+        <v>348</v>
+      </c>
+      <c r="U13" t="s">
+        <v>349</v>
+      </c>
+      <c r="V13" t="s">
+        <v>417</v>
+      </c>
+      <c r="W13" t="s">
+        <v>417</v>
+      </c>
+      <c r="X13" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>364</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA13"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="170">
+        <v>112</v>
+      </c>
+      <c r="B1" t="s" s="171">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s" s="172">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" t="s">
+        <v>366</v>
+      </c>
+      <c r="C11" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B12" t="s">
+        <v>366</v>
+      </c>
+      <c r="C12" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>411</v>
+      </c>
+      <c r="B13" t="s">
+        <v>366</v>
+      </c>
+      <c r="C13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" t="s">
+        <v>366</v>
+      </c>
+      <c r="C15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>378</v>
+      </c>
+      <c r="B16" t="s">
+        <v>366</v>
+      </c>
+      <c r="C16" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B17" t="s">
+        <v>366</v>
+      </c>
+      <c r="C17" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C18" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19" t="s">
+        <v>366</v>
+      </c>
+      <c r="C19" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" t="s">
+        <v>366</v>
+      </c>
+      <c r="C20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" t="s">
+        <v>366</v>
+      </c>
+      <c r="C21" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" t="s">
+        <v>366</v>
+      </c>
+      <c r="C23" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>199</v>
+      </c>
+      <c r="B24" t="s">
+        <v>366</v>
+      </c>
+      <c r="C24" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>391</v>
+      </c>
+      <c r="B25" t="s">
+        <v>366</v>
+      </c>
+      <c r="C25" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>329</v>
+      </c>
+      <c r="B26" t="s">
+        <v>366</v>
+      </c>
+      <c r="C26" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>330</v>
+      </c>
+      <c r="B27" t="s">
+        <v>366</v>
+      </c>
+      <c r="C27" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>395</v>
+      </c>
+      <c r="B28" t="s">
+        <v>366</v>
+      </c>
+      <c r="C28" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>218</v>
+      </c>
+      <c r="B29" t="s">
+        <v>366</v>
+      </c>
+      <c r="C29" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" t="s">
+        <v>366</v>
+      </c>
+      <c r="C30" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>224</v>
+      </c>
+      <c r="B31" t="s">
+        <v>366</v>
+      </c>
+      <c r="C31" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>400</v>
+      </c>
+      <c r="B32" t="s">
+        <v>366</v>
+      </c>
+      <c r="C32" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>331</v>
+      </c>
+      <c r="B34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>334</v>
+      </c>
+      <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>405</v>
+      </c>
+      <c r="B36" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>318</v>
+      </c>
+      <c r="B37"/>
+      <c r="C37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" t="s">
+        <v>407</v>
+      </c>
+      <c r="C38" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" t="s">
+        <v>409</v>
+      </c>
+      <c r="C39" t="s">
+        <v>410</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet156.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
@@ -3847,4 +8896,3206 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="90">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s" s="91">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="92">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s" s="93">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s" s="94">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s" s="95">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s" s="96">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s" s="97">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s" s="98">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s" s="99">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s" s="100">
+        <v>64</v>
+      </c>
+      <c r="J1" t="s" s="101">
+        <v>65</v>
+      </c>
+      <c r="K1" t="s" s="102">
+        <v>66</v>
+      </c>
+      <c r="L1" t="s" s="103">
+        <v>67</v>
+      </c>
+      <c r="M1" t="s" s="104">
+        <v>68</v>
+      </c>
+      <c r="N1" t="s" s="105">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4"/>
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9"/>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12"/>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14"/>
+      <c r="J14" t="s">
+        <v>90</v>
+      </c>
+      <c r="N14"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="106">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s" s="107">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s" s="108">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="109">
+        <v>112</v>
+      </c>
+      <c r="B1" t="s" s="110">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s" s="111">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="112">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s" s="113">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s" s="114">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s" s="115">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s" s="116">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s" s="117">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s" s="118">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s" s="119">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s" s="120">
+        <v>64</v>
+      </c>
+      <c r="J1" t="s" s="121">
+        <v>65</v>
+      </c>
+      <c r="K1" t="s" s="122">
+        <v>66</v>
+      </c>
+      <c r="L1" t="s" s="123">
+        <v>67</v>
+      </c>
+      <c r="M1" t="s" s="124">
+        <v>68</v>
+      </c>
+      <c r="N1" t="s" s="125">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>132</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s">
+        <v>136</v>
+      </c>
+      <c r="I14"/>
+      <c r="J14" t="s">
+        <v>90</v>
+      </c>
+      <c r="N14"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="126">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="127">
+        <v>112</v>
+      </c>
+      <c r="B1" t="s" s="128">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s" s="129">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="130">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s" s="131">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s" s="132">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s" s="133">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s" s="134">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s" s="135">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s" s="136">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s" s="137">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s" s="138">
+        <v>64</v>
+      </c>
+      <c r="J1" t="s" s="139">
+        <v>65</v>
+      </c>
+      <c r="K1" t="s" s="140">
+        <v>66</v>
+      </c>
+      <c r="L1" t="s" s="141">
+        <v>67</v>
+      </c>
+      <c r="M1" t="s" s="142">
+        <v>68</v>
+      </c>
+      <c r="N1" t="s" s="143">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4"/>
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J9"/>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>411</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>160</v>
+      </c>
+      <c r="I11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>329</v>
+      </c>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I13" t="s">
+        <v>208</v>
+      </c>
+      <c r="J13"/>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14" t="s">
+        <v>162</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>330</v>
+      </c>
+      <c r="I14"/>
+      <c r="J14"/>
+    </row>
+    <row r="15">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15" t="s">
+        <v>164</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" t="s">
+        <v>212</v>
+      </c>
+      <c r="J15"/>
+    </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16" t="s">
+        <v>166</v>
+      </c>
+      <c r="G16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" t="s">
+        <v>191</v>
+      </c>
+      <c r="J16"/>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17" t="s">
+        <v>168</v>
+      </c>
+      <c r="G17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17" t="s">
+        <v>194</v>
+      </c>
+      <c r="J17"/>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>224</v>
+      </c>
+      <c r="I18"/>
+      <c r="J18"/>
+    </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" t="s">
+        <v>331</v>
+      </c>
+      <c r="I19"/>
+      <c r="J19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" t="s">
+        <v>333</v>
+      </c>
+      <c r="D20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20"/>
+      <c r="J20"/>
+    </row>
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21"/>
+      <c r="J21"/>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" t="s">
+        <v>145</v>
+      </c>
+      <c r="I22"/>
+      <c r="J22"/>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>224</v>
+      </c>
+      <c r="I23"/>
+      <c r="J23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" t="s">
+        <v>334</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>335</v>
+      </c>
+      <c r="C25" t="s">
+        <v>336</v>
+      </c>
+      <c r="D25" t="s">
+        <v>321</v>
+      </c>
+      <c r="E25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25"/>
+      <c r="J25"/>
+    </row>
+    <row r="26">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26"/>
+      <c r="J26"/>
+    </row>
+    <row r="27">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G27" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" t="s">
+        <v>145</v>
+      </c>
+      <c r="I27"/>
+      <c r="J27"/>
+    </row>
+    <row r="28">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" t="s">
+        <v>148</v>
+      </c>
+      <c r="I28" t="s">
+        <v>149</v>
+      </c>
+      <c r="J28"/>
+    </row>
+    <row r="29">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" t="s">
+        <v>146</v>
+      </c>
+      <c r="I29" t="s">
+        <v>147</v>
+      </c>
+      <c r="J29"/>
+    </row>
+    <row r="30">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" t="s">
+        <v>150</v>
+      </c>
+      <c r="I30" t="s">
+        <v>151</v>
+      </c>
+      <c r="J30"/>
+    </row>
+    <row r="31">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" t="s">
+        <v>411</v>
+      </c>
+      <c r="I31"/>
+      <c r="J31"/>
+    </row>
+    <row r="32">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32" t="s">
+        <v>154</v>
+      </c>
+      <c r="G32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" t="s">
+        <v>160</v>
+      </c>
+      <c r="I32" t="s">
+        <v>165</v>
+      </c>
+      <c r="J32"/>
+    </row>
+    <row r="33">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33" t="s">
+        <v>157</v>
+      </c>
+      <c r="G33" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" t="s">
+        <v>329</v>
+      </c>
+      <c r="I33"/>
+      <c r="J33"/>
+    </row>
+    <row r="34">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34" t="s">
+        <v>159</v>
+      </c>
+      <c r="G34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" t="s">
+        <v>160</v>
+      </c>
+      <c r="I34" t="s">
+        <v>208</v>
+      </c>
+      <c r="J34"/>
+    </row>
+    <row r="35">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35" t="s">
+        <v>162</v>
+      </c>
+      <c r="G35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" t="s">
+        <v>330</v>
+      </c>
+      <c r="I35"/>
+      <c r="J35"/>
+    </row>
+    <row r="36">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36" t="s">
+        <v>164</v>
+      </c>
+      <c r="G36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" t="s">
+        <v>160</v>
+      </c>
+      <c r="I36" t="s">
+        <v>212</v>
+      </c>
+      <c r="J36"/>
+    </row>
+    <row r="37">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37" t="s">
+        <v>166</v>
+      </c>
+      <c r="G37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" t="s">
+        <v>190</v>
+      </c>
+      <c r="I37" t="s">
+        <v>191</v>
+      </c>
+      <c r="J37"/>
+    </row>
+    <row r="38">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38" t="s">
+        <v>168</v>
+      </c>
+      <c r="G38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" t="s">
+        <v>224</v>
+      </c>
+      <c r="I38"/>
+      <c r="J38"/>
+    </row>
+    <row r="39">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" t="s">
+        <v>334</v>
+      </c>
+      <c r="I39"/>
+      <c r="J39" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" t="s">
+        <v>337</v>
+      </c>
+      <c r="C40" t="s">
+        <v>338</v>
+      </c>
+      <c r="D40" t="s">
+        <v>322</v>
+      </c>
+      <c r="E40" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" t="s">
+        <v>71</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40"/>
+    </row>
+    <row r="41">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" t="s">
+        <v>6</v>
+      </c>
+      <c r="I41"/>
+      <c r="J41"/>
+    </row>
+    <row r="42">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42" t="s">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" t="s">
+        <v>145</v>
+      </c>
+      <c r="I42"/>
+      <c r="J42"/>
+    </row>
+    <row r="43">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43" t="s">
+        <v>81</v>
+      </c>
+      <c r="G43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" t="s">
+        <v>148</v>
+      </c>
+      <c r="I43" t="s">
+        <v>149</v>
+      </c>
+      <c r="J43"/>
+    </row>
+    <row r="44">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" t="s">
+        <v>146</v>
+      </c>
+      <c r="I44" t="s">
+        <v>147</v>
+      </c>
+      <c r="J44"/>
+    </row>
+    <row r="45">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45" t="s">
+        <v>86</v>
+      </c>
+      <c r="G45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" t="s">
+        <v>150</v>
+      </c>
+      <c r="I45" t="s">
+        <v>151</v>
+      </c>
+      <c r="J45"/>
+    </row>
+    <row r="46">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" t="s">
+        <v>411</v>
+      </c>
+      <c r="I46"/>
+      <c r="J46"/>
+    </row>
+    <row r="47">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" t="s">
+        <v>160</v>
+      </c>
+      <c r="I47" t="s">
+        <v>165</v>
+      </c>
+      <c r="J47"/>
+    </row>
+    <row r="48">
+      <c r="A48"/>
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48" t="s">
+        <v>157</v>
+      </c>
+      <c r="G48" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" t="s">
+        <v>329</v>
+      </c>
+      <c r="I48"/>
+      <c r="J48"/>
+    </row>
+    <row r="49">
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49" t="s">
+        <v>159</v>
+      </c>
+      <c r="G49" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" t="s">
+        <v>160</v>
+      </c>
+      <c r="I49" t="s">
+        <v>208</v>
+      </c>
+      <c r="J49"/>
+    </row>
+    <row r="50">
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50" t="s">
+        <v>162</v>
+      </c>
+      <c r="G50" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" t="s">
+        <v>330</v>
+      </c>
+      <c r="I50"/>
+      <c r="J50"/>
+    </row>
+    <row r="51">
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51" t="s">
+        <v>164</v>
+      </c>
+      <c r="G51" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" t="s">
+        <v>160</v>
+      </c>
+      <c r="I51" t="s">
+        <v>212</v>
+      </c>
+      <c r="J51"/>
+    </row>
+    <row r="52">
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52" t="s">
+        <v>166</v>
+      </c>
+      <c r="G52" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" t="s">
+        <v>193</v>
+      </c>
+      <c r="I52" t="s">
+        <v>194</v>
+      </c>
+      <c r="J52"/>
+    </row>
+    <row r="53">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53" t="s">
+        <v>168</v>
+      </c>
+      <c r="G53" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" t="s">
+        <v>224</v>
+      </c>
+      <c r="I53"/>
+      <c r="J53"/>
+    </row>
+    <row r="54">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54" t="s">
+        <v>170</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" t="s">
+        <v>334</v>
+      </c>
+      <c r="I54"/>
+      <c r="J54" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" t="s">
+        <v>339</v>
+      </c>
+      <c r="C55" t="s">
+        <v>340</v>
+      </c>
+      <c r="D55" t="s">
+        <v>323</v>
+      </c>
+      <c r="E55" t="s">
+        <v>70</v>
+      </c>
+      <c r="F55" t="s">
+        <v>75</v>
+      </c>
+      <c r="G55" t="s">
+        <v>126</v>
+      </c>
+      <c r="H55" t="s">
+        <v>71</v>
+      </c>
+      <c r="I55"/>
+      <c r="J55"/>
+    </row>
+    <row r="56">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56" t="s">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" t="s">
+        <v>6</v>
+      </c>
+      <c r="I56"/>
+      <c r="J56"/>
+    </row>
+    <row r="57">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57" t="s">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" t="s">
+        <v>145</v>
+      </c>
+      <c r="I57"/>
+      <c r="J57"/>
+    </row>
+    <row r="58">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58" t="s">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" t="s">
+        <v>148</v>
+      </c>
+      <c r="I58" t="s">
+        <v>149</v>
+      </c>
+      <c r="J58"/>
+    </row>
+    <row r="59">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59" t="s">
+        <v>84</v>
+      </c>
+      <c r="G59" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" t="s">
+        <v>146</v>
+      </c>
+      <c r="I59" t="s">
+        <v>147</v>
+      </c>
+      <c r="J59"/>
+    </row>
+    <row r="60">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60" t="s">
+        <v>86</v>
+      </c>
+      <c r="G60" t="s">
+        <v>34</v>
+      </c>
+      <c r="H60" t="s">
+        <v>150</v>
+      </c>
+      <c r="I60" t="s">
+        <v>151</v>
+      </c>
+      <c r="J60"/>
+    </row>
+    <row r="61">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G61" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61" t="s">
+        <v>411</v>
+      </c>
+      <c r="I61"/>
+      <c r="J61"/>
+    </row>
+    <row r="62">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62" t="s">
+        <v>154</v>
+      </c>
+      <c r="G62" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" t="s">
+        <v>160</v>
+      </c>
+      <c r="I62" t="s">
+        <v>165</v>
+      </c>
+      <c r="J62"/>
+    </row>
+    <row r="63">
+      <c r="A63"/>
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63" t="s">
+        <v>157</v>
+      </c>
+      <c r="G63" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63" t="s">
+        <v>329</v>
+      </c>
+      <c r="I63"/>
+      <c r="J63"/>
+    </row>
+    <row r="64">
+      <c r="A64"/>
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64" t="s">
+        <v>159</v>
+      </c>
+      <c r="G64" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" t="s">
+        <v>160</v>
+      </c>
+      <c r="I64" t="s">
+        <v>208</v>
+      </c>
+      <c r="J64"/>
+    </row>
+    <row r="65">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65" t="s">
+        <v>162</v>
+      </c>
+      <c r="G65" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" t="s">
+        <v>330</v>
+      </c>
+      <c r="I65"/>
+      <c r="J65"/>
+    </row>
+    <row r="66">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66" t="s">
+        <v>164</v>
+      </c>
+      <c r="G66" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" t="s">
+        <v>160</v>
+      </c>
+      <c r="I66" t="s">
+        <v>212</v>
+      </c>
+      <c r="J66"/>
+    </row>
+    <row r="67">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67" t="s">
+        <v>166</v>
+      </c>
+      <c r="G67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" t="s">
+        <v>155</v>
+      </c>
+      <c r="I67" t="s">
+        <v>156</v>
+      </c>
+      <c r="J67"/>
+    </row>
+    <row r="68">
+      <c r="A68"/>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68" t="s">
+        <v>168</v>
+      </c>
+      <c r="G68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" t="s">
+        <v>224</v>
+      </c>
+      <c r="I68"/>
+      <c r="J68"/>
+    </row>
+    <row r="69">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69" t="s">
+        <v>170</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" t="s">
+        <v>334</v>
+      </c>
+      <c r="I69"/>
+      <c r="J69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>341</v>
+      </c>
+      <c r="C70" t="s">
+        <v>412</v>
+      </c>
+      <c r="D70" t="s">
+        <v>413</v>
+      </c>
+      <c r="E70" t="s">
+        <v>70</v>
+      </c>
+      <c r="F70" t="s">
+        <v>75</v>
+      </c>
+      <c r="G70" t="s">
+        <v>126</v>
+      </c>
+      <c r="H70" t="s">
+        <v>71</v>
+      </c>
+      <c r="I70"/>
+      <c r="J70"/>
+    </row>
+    <row r="71">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71" t="s">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+      <c r="H71" t="s">
+        <v>6</v>
+      </c>
+      <c r="I71"/>
+      <c r="J71"/>
+    </row>
+    <row r="72">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72" t="s">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" t="s">
+        <v>145</v>
+      </c>
+      <c r="I72"/>
+      <c r="J72"/>
+    </row>
+    <row r="73">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73" t="s">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" t="s">
+        <v>148</v>
+      </c>
+      <c r="I73" t="s">
+        <v>149</v>
+      </c>
+      <c r="J73"/>
+    </row>
+    <row r="74">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74" t="s">
+        <v>34</v>
+      </c>
+      <c r="H74" t="s">
+        <v>146</v>
+      </c>
+      <c r="I74" t="s">
+        <v>147</v>
+      </c>
+      <c r="J74"/>
+    </row>
+    <row r="75">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75" t="s">
+        <v>86</v>
+      </c>
+      <c r="G75" t="s">
+        <v>34</v>
+      </c>
+      <c r="H75" t="s">
+        <v>150</v>
+      </c>
+      <c r="I75" t="s">
+        <v>151</v>
+      </c>
+      <c r="J75"/>
+    </row>
+    <row r="76">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76" t="s">
+        <v>88</v>
+      </c>
+      <c r="G76" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" t="s">
+        <v>411</v>
+      </c>
+      <c r="I76"/>
+      <c r="J76"/>
+    </row>
+    <row r="77">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77" t="s">
+        <v>154</v>
+      </c>
+      <c r="G77" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" t="s">
+        <v>160</v>
+      </c>
+      <c r="I77" t="s">
+        <v>165</v>
+      </c>
+      <c r="J77"/>
+    </row>
+    <row r="78">
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78"/>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78" t="s">
+        <v>157</v>
+      </c>
+      <c r="G78" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" t="s">
+        <v>329</v>
+      </c>
+      <c r="I78"/>
+      <c r="J78"/>
+    </row>
+    <row r="79">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79" t="s">
+        <v>159</v>
+      </c>
+      <c r="G79" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" t="s">
+        <v>160</v>
+      </c>
+      <c r="I79" t="s">
+        <v>208</v>
+      </c>
+      <c r="J79"/>
+    </row>
+    <row r="80">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80" t="s">
+        <v>162</v>
+      </c>
+      <c r="G80" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" t="s">
+        <v>330</v>
+      </c>
+      <c r="I80"/>
+      <c r="J80"/>
+    </row>
+    <row r="81">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81" t="s">
+        <v>164</v>
+      </c>
+      <c r="G81" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" t="s">
+        <v>160</v>
+      </c>
+      <c r="I81" t="s">
+        <v>212</v>
+      </c>
+      <c r="J81"/>
+    </row>
+    <row r="82">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82" t="s">
+        <v>166</v>
+      </c>
+      <c r="G82" t="s">
+        <v>34</v>
+      </c>
+      <c r="H82" t="s">
+        <v>190</v>
+      </c>
+      <c r="I82" t="s">
+        <v>191</v>
+      </c>
+      <c r="J82"/>
+    </row>
+    <row r="83">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83" t="s">
+        <v>168</v>
+      </c>
+      <c r="G83" t="s">
+        <v>34</v>
+      </c>
+      <c r="H83" t="s">
+        <v>193</v>
+      </c>
+      <c r="I83" t="s">
+        <v>194</v>
+      </c>
+      <c r="J83"/>
+    </row>
+    <row r="84">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84" t="s">
+        <v>170</v>
+      </c>
+      <c r="G84" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" t="s">
+        <v>224</v>
+      </c>
+      <c r="I84"/>
+      <c r="J84"/>
+    </row>
+    <row r="85">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85" t="s">
+        <v>173</v>
+      </c>
+      <c r="G85" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85" t="s">
+        <v>331</v>
+      </c>
+      <c r="I85"/>
+      <c r="J85" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>70</v>
+      </c>
+      <c r="B86" t="s">
+        <v>414</v>
+      </c>
+      <c r="C86" t="s">
+        <v>415</v>
+      </c>
+      <c r="D86" t="s">
+        <v>416</v>
+      </c>
+      <c r="E86" t="s">
+        <v>70</v>
+      </c>
+      <c r="F86" t="s">
+        <v>75</v>
+      </c>
+      <c r="G86" t="s">
+        <v>126</v>
+      </c>
+      <c r="H86" t="s">
+        <v>71</v>
+      </c>
+      <c r="I86"/>
+      <c r="J86"/>
+    </row>
+    <row r="87">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87" t="s">
+        <v>76</v>
+      </c>
+      <c r="G87" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" t="s">
+        <v>6</v>
+      </c>
+      <c r="I87"/>
+      <c r="J87"/>
+    </row>
+    <row r="88">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88" t="s">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" t="s">
+        <v>145</v>
+      </c>
+      <c r="I88"/>
+      <c r="J88"/>
+    </row>
+    <row r="89">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89" t="s">
+        <v>81</v>
+      </c>
+      <c r="G89" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" t="s">
+        <v>148</v>
+      </c>
+      <c r="I89" t="s">
+        <v>149</v>
+      </c>
+      <c r="J89"/>
+    </row>
+    <row r="90">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90" t="s">
+        <v>84</v>
+      </c>
+      <c r="G90" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" t="s">
+        <v>146</v>
+      </c>
+      <c r="I90" t="s">
+        <v>147</v>
+      </c>
+      <c r="J90"/>
+    </row>
+    <row r="91">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91" t="s">
+        <v>86</v>
+      </c>
+      <c r="G91" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" t="s">
+        <v>150</v>
+      </c>
+      <c r="I91" t="s">
+        <v>151</v>
+      </c>
+      <c r="J91"/>
+    </row>
+    <row r="92">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92" t="s">
+        <v>88</v>
+      </c>
+      <c r="G92" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" t="s">
+        <v>411</v>
+      </c>
+      <c r="I92"/>
+      <c r="J92"/>
+    </row>
+    <row r="93">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93"/>
+      <c r="F93" t="s">
+        <v>154</v>
+      </c>
+      <c r="G93" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93" t="s">
+        <v>160</v>
+      </c>
+      <c r="I93" t="s">
+        <v>165</v>
+      </c>
+      <c r="J93"/>
+    </row>
+    <row r="94">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94" t="s">
+        <v>157</v>
+      </c>
+      <c r="G94" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" t="s">
+        <v>329</v>
+      </c>
+      <c r="I94"/>
+      <c r="J94"/>
+    </row>
+    <row r="95">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95" t="s">
+        <v>159</v>
+      </c>
+      <c r="G95" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95" t="s">
+        <v>160</v>
+      </c>
+      <c r="I95" t="s">
+        <v>208</v>
+      </c>
+      <c r="J95"/>
+    </row>
+    <row r="96">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96" t="s">
+        <v>162</v>
+      </c>
+      <c r="G96" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" t="s">
+        <v>330</v>
+      </c>
+      <c r="I96"/>
+      <c r="J96"/>
+    </row>
+    <row r="97">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97" t="s">
+        <v>164</v>
+      </c>
+      <c r="G97" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97" t="s">
+        <v>160</v>
+      </c>
+      <c r="I97" t="s">
+        <v>212</v>
+      </c>
+      <c r="J97"/>
+    </row>
+    <row r="98">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98" t="s">
+        <v>166</v>
+      </c>
+      <c r="G98" t="s">
+        <v>34</v>
+      </c>
+      <c r="H98" t="s">
+        <v>190</v>
+      </c>
+      <c r="I98" t="s">
+        <v>191</v>
+      </c>
+      <c r="J98"/>
+    </row>
+    <row r="99">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99" t="s">
+        <v>168</v>
+      </c>
+      <c r="G99" t="s">
+        <v>34</v>
+      </c>
+      <c r="H99" t="s">
+        <v>193</v>
+      </c>
+      <c r="I99" t="s">
+        <v>194</v>
+      </c>
+      <c r="J99"/>
+    </row>
+    <row r="100">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100" t="s">
+        <v>170</v>
+      </c>
+      <c r="G100" t="s">
+        <v>20</v>
+      </c>
+      <c r="H100" t="s">
+        <v>224</v>
+      </c>
+      <c r="I100"/>
+      <c r="J100"/>
+    </row>
+    <row r="101">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101" t="s">
+        <v>173</v>
+      </c>
+      <c r="G101" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101" t="s">
+        <v>334</v>
+      </c>
+      <c r="I101"/>
+      <c r="J101" t="s">
+        <v>343</v>
+      </c>
+      <c r="N101"/>
+    </row>
+  </sheetData>
+</worksheet>
 </file>